--- a/Notas - 1º etapa.xlsx
+++ b/Notas - 1º etapa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polia\OneDrive\Desktop\Edgar da Mata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211218DB-0019-488E-A822-80BE82963F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E38DBC1-5D28-48E1-8A65-61AEB36EAE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FE5C7E3B-0CF7-4B17-BC8B-315FA1CE83BF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FE5C7E3B-0CF7-4B17-BC8B-315FA1CE83BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="84">
   <si>
     <t>Nº</t>
   </si>
@@ -160,9 +160,6 @@
     <t>Recuperação</t>
   </si>
   <si>
-    <t>Distribuição: Caderno 5pts | 3 Para Casa Avaliativos 5 pontos | Livro 5pts | Comportamento 5 pts | Avaliação 10 pts</t>
-  </si>
-  <si>
     <t>ALICE EMANUELLY CARLOS AMORIM</t>
   </si>
   <si>
@@ -271,9 +268,6 @@
     <t>Trabalho Água</t>
   </si>
   <si>
-    <t>Distribuição: Maquete 10 pts | Trabalho Água 5 pontos | Comportamento 5 pts | Avaliação 10 pts</t>
-  </si>
-  <si>
     <t>CIÊNCIAS  - 1º ETAPA - 4ºB</t>
   </si>
   <si>
@@ -281,13 +275,31 @@
   </si>
   <si>
     <t>MATEMÁTICA - 1º ETAPA -4º A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>Distribuição: Caderno- 5 pontos | 3 Para Casa Avaliativos - 5 pontos | Livro - 5 pontos | Comportamento - 5 pontos | Avaliação - 10 pontos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professora: Poliana Camila Rocha de Melo </t>
+  </si>
+  <si>
+    <t>Distribuição: Caderno - 5 pontos | 1 Para Casa Avaliativo -  5 pontos | Livro - 5 pontos | Comportamento - 5 pontos | Avaliação -10 pontos</t>
+  </si>
+  <si>
+    <t>Distribuição: Maquete - 10 pontos | Trabalho Água -  5 pontos | Comportamento - 5 pontos | Avaliação - 10 pontos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -295,8 +307,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -312,6 +332,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -343,7 +369,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -355,11 +381,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -695,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{265D5763-796C-4A95-880D-F96959D985BE}">
-  <dimension ref="A3:K38"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
@@ -707,23 +737,37 @@
     <col min="9" max="9" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
+    <row r="1" spans="1:11" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+    </row>
+    <row r="3" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -819,7 +863,9 @@
       <c r="H7" s="2">
         <v>12</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="2">
+        <v>18</v>
+      </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
@@ -877,7 +923,9 @@
       <c r="H9" s="2">
         <v>5</v>
       </c>
-      <c r="I9" s="1"/>
+      <c r="I9" s="7">
+        <v>9</v>
+      </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
     </row>
@@ -906,7 +954,9 @@
       <c r="H10" s="2">
         <v>12.5</v>
       </c>
-      <c r="I10" s="1"/>
+      <c r="I10" s="7">
+        <v>17.5</v>
+      </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
     </row>
@@ -964,7 +1014,9 @@
       <c r="H12" s="2">
         <v>6.5</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="7">
+        <v>11.5</v>
+      </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
@@ -1022,7 +1074,9 @@
       <c r="H14" s="2">
         <v>5</v>
       </c>
-      <c r="I14" s="1"/>
+      <c r="I14" s="7">
+        <v>10</v>
+      </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
@@ -1080,7 +1134,9 @@
       <c r="H16" s="2">
         <v>11</v>
       </c>
-      <c r="I16" s="1"/>
+      <c r="I16" s="2">
+        <v>18</v>
+      </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
@@ -1109,7 +1165,9 @@
       <c r="H17" s="2">
         <v>8</v>
       </c>
-      <c r="I17" s="1"/>
+      <c r="I17" s="7">
+        <v>13</v>
+      </c>
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
     </row>
@@ -1123,8 +1181,12 @@
       <c r="C18" s="2">
         <v>2</v>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
       <c r="F18" s="2">
         <v>4</v>
       </c>
@@ -1132,9 +1194,11 @@
         <v>3</v>
       </c>
       <c r="H18" s="2">
-        <v>9</v>
-      </c>
-      <c r="I18" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="I18" s="7">
+        <v>15</v>
+      </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
@@ -1163,7 +1227,7 @@
       <c r="H19" s="2">
         <v>17.5</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19" s="2">
         <v>18</v>
       </c>
       <c r="J19" s="6"/>
@@ -1194,7 +1258,7 @@
       <c r="H20" s="2">
         <v>16.5</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="2">
         <v>18</v>
       </c>
       <c r="J20" s="6"/>
@@ -1225,7 +1289,9 @@
       <c r="H21" s="2">
         <v>1</v>
       </c>
-      <c r="I21" s="1"/>
+      <c r="I21" s="7">
+        <v>6</v>
+      </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
     </row>
@@ -1301,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2">
         <v>4</v>
@@ -1310,9 +1376,11 @@
         <v>4</v>
       </c>
       <c r="H24" s="2">
-        <v>9</v>
-      </c>
-      <c r="I24" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="I24" s="7">
+        <v>16</v>
+      </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
     </row>
@@ -1333,15 +1401,17 @@
         <v>0</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
       </c>
       <c r="H25" s="2">
-        <v>1</v>
-      </c>
-      <c r="I25" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I25" s="7">
+        <v>7</v>
+      </c>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
     </row>
@@ -1362,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2">
         <v>2.5</v>
@@ -1370,7 +1440,9 @@
       <c r="H26" s="2">
         <v>3</v>
       </c>
-      <c r="I26" s="1"/>
+      <c r="I26" s="7">
+        <v>12</v>
+      </c>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
     </row>
@@ -1399,7 +1471,9 @@
       <c r="H27" s="2">
         <v>11.5</v>
       </c>
-      <c r="I27" s="1"/>
+      <c r="I27" s="7">
+        <v>16.5</v>
+      </c>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
     </row>
@@ -1428,7 +1502,9 @@
       <c r="H28" s="2">
         <v>13</v>
       </c>
-      <c r="I28" s="1"/>
+      <c r="I28" s="2">
+        <v>18</v>
+      </c>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
@@ -1457,7 +1533,9 @@
       <c r="H29" s="2">
         <v>14</v>
       </c>
-      <c r="I29" s="1"/>
+      <c r="I29" s="7">
+        <v>17</v>
+      </c>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
@@ -1486,7 +1564,9 @@
       <c r="H30" s="2">
         <v>10.5</v>
       </c>
-      <c r="I30" s="1"/>
+      <c r="I30" s="7">
+        <v>14.5</v>
+      </c>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
     </row>
@@ -1573,7 +1653,9 @@
       <c r="H33" s="2">
         <v>4</v>
       </c>
-      <c r="I33" s="1"/>
+      <c r="I33" s="7">
+        <v>9</v>
+      </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
     </row>
@@ -1602,7 +1684,7 @@
       <c r="H34" s="2">
         <v>16</v>
       </c>
-      <c r="I34" s="3">
+      <c r="I34" s="2">
         <v>18</v>
       </c>
       <c r="J34" s="6"/>
@@ -1633,8 +1715,8 @@
       <c r="H35" s="2">
         <v>7</v>
       </c>
-      <c r="I35" s="1">
-        <v>7</v>
+      <c r="I35" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
@@ -1685,9 +1767,10 @@
       <c r="K38" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -1695,409 +1778,410 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22808D7A-FF36-43BE-917F-22779B1C1497}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="18.21875" customWidth="1"/>
     <col min="8" max="8" width="14.21875" customWidth="1"/>
     <col min="9" max="9" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="1" spans="1:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+    </row>
+    <row r="2" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="3" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1">
-        <v>5</v>
-      </c>
-      <c r="G4" s="1">
-        <v>8</v>
-      </c>
-      <c r="H4" s="1">
-        <v>25</v>
-      </c>
-      <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>5</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5</v>
+      </c>
+      <c r="G5" s="1">
+        <v>8</v>
+      </c>
+      <c r="H5" s="1">
+        <v>25</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>6</v>
+      </c>
+      <c r="H6" s="2">
+        <v>17</v>
+      </c>
+      <c r="I6" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="3">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>6</v>
-      </c>
-      <c r="H5" s="3">
-        <v>17</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4</v>
+      </c>
+      <c r="H7" s="2">
+        <v>15</v>
+      </c>
+      <c r="I7" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="3">
-        <v>3</v>
-      </c>
-      <c r="D6" s="3">
-        <v>3</v>
-      </c>
-      <c r="E6" s="3">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>4</v>
-      </c>
-      <c r="H6" s="3">
-        <v>15</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="I8" s="2">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="3">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3">
-        <v>4</v>
-      </c>
-      <c r="E7" s="3">
-        <v>3</v>
-      </c>
-      <c r="F7" s="3">
-        <v>5</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H7" s="3">
-        <v>15.5</v>
-      </c>
-      <c r="I7" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="3">
-        <v>5</v>
-      </c>
-      <c r="D8" s="3">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>8.5</v>
-      </c>
-      <c r="H8" s="3">
-        <v>20.5</v>
-      </c>
-      <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="3">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="H9" s="3">
+        <v>20.5</v>
+      </c>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="3">
+        <v>5</v>
+      </c>
+      <c r="D10" s="3">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
+        <v>18</v>
+      </c>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3">
-        <v>18</v>
-      </c>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="2">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
-        <v>3</v>
-      </c>
-      <c r="H10" s="2">
-        <v>10</v>
-      </c>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="3">
-        <v>3</v>
-      </c>
-      <c r="D11" s="3">
-        <v>5</v>
-      </c>
-      <c r="E11" s="3">
-        <v>5</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3">
-        <v>7</v>
-      </c>
-      <c r="H11" s="3">
-        <v>20</v>
-      </c>
-      <c r="I11" s="1"/>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>3</v>
+      </c>
+      <c r="H11" s="2">
+        <v>10</v>
+      </c>
+      <c r="I11" s="7">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>7</v>
+      </c>
+      <c r="H12" s="3">
+        <v>20</v>
+      </c>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3</v>
+      </c>
+      <c r="D13" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>5</v>
+      </c>
+      <c r="F13" s="3">
+        <v>5</v>
+      </c>
+      <c r="G13" s="3">
+        <v>9</v>
+      </c>
+      <c r="H13" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="3">
-        <v>3</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>3</v>
+      </c>
+      <c r="H14" s="2">
+        <v>12</v>
+      </c>
+      <c r="I14" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
         <v>4.5</v>
       </c>
-      <c r="E12" s="3">
-        <v>5</v>
-      </c>
-      <c r="F12" s="3">
-        <v>5</v>
-      </c>
-      <c r="G12" s="3">
-        <v>9</v>
-      </c>
-      <c r="H12" s="3">
-        <v>26.5</v>
-      </c>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2">
-        <v>3</v>
-      </c>
-      <c r="H13" s="2">
-        <v>12</v>
-      </c>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="3">
-        <v>3</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
         <v>8.5</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H15" s="2">
         <v>17</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I15" s="2">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3">
-        <v>5</v>
-      </c>
-      <c r="G15" s="3">
-        <v>8</v>
-      </c>
-      <c r="H15" s="3">
-        <v>23</v>
-      </c>
-      <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C16" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="3">
         <v>4</v>
       </c>
       <c r="E16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" s="3">
         <v>5</v>
@@ -2106,49 +2190,49 @@
         <v>8</v>
       </c>
       <c r="H16" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C17" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17" s="3">
         <v>5</v>
       </c>
       <c r="G17" s="3">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="H17" s="3">
-        <v>26.5</v>
+        <v>24</v>
       </c>
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C18" s="3">
         <v>4</v>
       </c>
       <c r="D18" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="3">
         <v>5</v>
@@ -2160,78 +2244,78 @@
         <v>9.5</v>
       </c>
       <c r="H18" s="3">
-        <v>28.5</v>
+        <v>26.5</v>
       </c>
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="3">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3">
+        <v>5</v>
+      </c>
+      <c r="E19" s="3">
+        <v>5</v>
+      </c>
+      <c r="F19" s="3">
+        <v>5</v>
+      </c>
+      <c r="G19" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="H19" s="3">
+        <v>28.5</v>
+      </c>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="3">
-        <v>3</v>
-      </c>
-      <c r="D19" s="3">
-        <v>2</v>
-      </c>
-      <c r="E19" s="3">
-        <v>5</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3">
+      <c r="B20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2">
+        <v>5</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
         <v>7</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H20" s="2">
         <v>17</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I20" s="2">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="3">
-        <v>3</v>
-      </c>
-      <c r="D20" s="3">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3">
-        <v>7.5</v>
-      </c>
-      <c r="H20" s="3">
-        <v>23.5</v>
-      </c>
-      <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C21" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" s="3">
         <v>5</v>
@@ -2240,25 +2324,25 @@
         <v>5</v>
       </c>
       <c r="G21" s="3">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="H21" s="3">
-        <v>26</v>
+        <v>23.5</v>
       </c>
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C22" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="3">
         <v>5</v>
@@ -2267,337 +2351,374 @@
         <v>5</v>
       </c>
       <c r="G22" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H22" s="3">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3">
+        <v>7</v>
+      </c>
+      <c r="H23" s="3">
+        <v>20</v>
+      </c>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="3">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>25.5</v>
+      </c>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="3">
-        <v>3</v>
-      </c>
-      <c r="D23" s="3">
-        <v>4</v>
-      </c>
-      <c r="E23" s="3">
-        <v>4</v>
-      </c>
-      <c r="F23" s="3">
-        <v>5</v>
-      </c>
-      <c r="G23" s="3">
-        <v>9.5</v>
-      </c>
-      <c r="H23" s="3">
-        <v>25.5</v>
-      </c>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="2">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2">
-        <v>3</v>
-      </c>
-      <c r="E24" s="2">
-        <v>4</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2">
-        <v>4</v>
-      </c>
-      <c r="H24" s="2">
+      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3</v>
+      </c>
+      <c r="E25" s="2">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>4</v>
+      </c>
+      <c r="H25" s="2">
         <v>14</v>
       </c>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="3">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3">
-        <v>2</v>
-      </c>
-      <c r="E25" s="3">
-        <v>2</v>
-      </c>
-      <c r="F25" s="3">
-        <v>5</v>
-      </c>
-      <c r="G25" s="3">
-        <v>5</v>
-      </c>
-      <c r="H25" s="3">
-        <v>15</v>
-      </c>
-      <c r="I25" s="1">
+      <c r="I25" s="2">
         <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2">
+        <v>5</v>
+      </c>
+      <c r="H26" s="2">
+        <v>15</v>
+      </c>
+      <c r="I26" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2">
+        <v>7</v>
+      </c>
+      <c r="I27" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="2">
-        <v>2</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="C28" s="3">
         <v>1</v>
       </c>
-      <c r="E26" s="2">
-        <v>3</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2">
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
+        <v>5</v>
+      </c>
+      <c r="F28" s="3">
+        <v>5</v>
+      </c>
+      <c r="G28" s="3">
+        <v>8</v>
+      </c>
+      <c r="H28" s="3">
+        <v>19</v>
+      </c>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="2">
         <v>1</v>
       </c>
-      <c r="H26" s="2">
-        <v>7</v>
-      </c>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="3">
+      <c r="D29" s="2">
         <v>1</v>
       </c>
-      <c r="D27" s="3">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3">
-        <v>5</v>
-      </c>
-      <c r="F27" s="3">
-        <v>5</v>
-      </c>
-      <c r="G27" s="3">
-        <v>8</v>
-      </c>
-      <c r="H27" s="3">
-        <v>19</v>
-      </c>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="E29" s="2">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2">
+        <v>5</v>
+      </c>
+      <c r="G29" s="2">
         <v>1</v>
       </c>
-      <c r="D28" s="2">
-        <v>1</v>
-      </c>
-      <c r="E28" s="2">
-        <v>4</v>
-      </c>
-      <c r="F28" s="2">
-        <v>5</v>
-      </c>
-      <c r="G28" s="2">
-        <v>1</v>
-      </c>
-      <c r="H28" s="2">
+      <c r="H29" s="2">
         <v>13</v>
       </c>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="3">
-        <v>3</v>
-      </c>
-      <c r="D29" s="3">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3">
-        <v>18</v>
-      </c>
-      <c r="I29" s="1"/>
+      <c r="I29" s="7">
+        <v>17</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C30" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="3">
         <v>4</v>
       </c>
       <c r="F30" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G30" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H30" s="3">
         <v>18</v>
       </c>
-      <c r="I30" s="3"/>
+      <c r="I30" s="1"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C31" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D31" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" s="3">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F31" s="3">
         <v>5</v>
       </c>
       <c r="G31" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H31" s="3">
-        <v>22.5</v>
-      </c>
-      <c r="I31" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="3">
+        <v>2</v>
+      </c>
+      <c r="D32" s="3">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="F32" s="3">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3">
+        <v>7</v>
+      </c>
+      <c r="H32" s="3">
+        <v>22.5</v>
+      </c>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="1">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1">
+        <v>5</v>
+      </c>
+      <c r="F33" s="1">
+        <v>5</v>
+      </c>
+      <c r="G33" s="1">
+        <v>5</v>
+      </c>
+      <c r="H33" s="1">
+        <v>21</v>
+      </c>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="1">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1">
-        <v>5</v>
-      </c>
-      <c r="F32" s="1">
-        <v>5</v>
-      </c>
-      <c r="G32" s="1">
-        <v>5</v>
-      </c>
-      <c r="H32" s="1">
-        <v>21</v>
-      </c>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="2">
+      <c r="C34" s="2">
         <v>1</v>
       </c>
-      <c r="D33" s="2">
-        <v>0</v>
-      </c>
-      <c r="E33" s="2">
-        <v>2</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2">
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2">
+        <v>3</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2">
         <v>2.5</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H34" s="2">
         <v>5.5</v>
       </c>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="I34" s="7">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B05A61D-8986-40ED-93C5-768E17F97F81}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.77734375" customWidth="1"/>
@@ -2605,552 +2726,860 @@
     <col min="4" max="4" width="12.77734375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="1" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="3" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3">
-        <v>4</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1">
+        <v>5</v>
+      </c>
+      <c r="F5" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G5" s="1">
+        <f>C5+D5+E5+F5</f>
+        <v>27.5</v>
+      </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="C6" s="1">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4</v>
+      </c>
       <c r="E6" s="3">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F6" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" ref="G6:G35" si="0">C6+D6+E6+F6</f>
+        <v>27.5</v>
+      </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4</v>
+      </c>
       <c r="E7" s="3">
-        <v>3</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="0"/>
+        <v>22.5</v>
+      </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="C8" s="1">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
       <c r="E8" s="3">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
+        <v>6</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="1">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3">
+        <v>6</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="3">
+        <v>10</v>
+      </c>
+      <c r="D10" s="3">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="C11" s="3">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="3">
+        <v>10</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="3">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>5</v>
+      </c>
+      <c r="F13" s="3">
+        <v>9</v>
+      </c>
+      <c r="G13" s="3">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="3">
+        <v>10</v>
+      </c>
+      <c r="D14" s="3">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>6</v>
+      </c>
+      <c r="G14" s="3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="3">
+        <v>10</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="F15" s="3">
+        <v>6</v>
+      </c>
+      <c r="G15" s="3">
+        <f t="shared" si="0"/>
+        <v>25.5</v>
+      </c>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="3">
+        <v>10</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>5</v>
+      </c>
+      <c r="F16" s="3">
+        <v>6</v>
+      </c>
+      <c r="G16" s="3">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="3">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="D17" s="3">
+        <v>4</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4</v>
+      </c>
+      <c r="F17" s="3">
+        <v>6</v>
+      </c>
+      <c r="G17" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="3">
+        <v>10</v>
+      </c>
+      <c r="D18" s="3">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
+        <v>10</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="3">
+        <v>10</v>
+      </c>
+      <c r="D19" s="3">
+        <v>5</v>
+      </c>
+      <c r="E19" s="3">
+        <v>5</v>
+      </c>
+      <c r="F19" s="3">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3">
-        <v>5</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3">
-        <v>5</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3">
-        <v>4</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="G19" s="3">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="C20" s="3">
+        <v>10</v>
+      </c>
+      <c r="D20" s="3">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
+        <v>6</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3">
-        <v>5</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="C21" s="3">
+        <v>10</v>
+      </c>
+      <c r="D21" s="3">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="C22" s="3">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" si="0"/>
+        <v>28.5</v>
+      </c>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="C23" s="3">
+        <v>10</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="G23" s="3">
+        <f t="shared" si="0"/>
+        <v>21.5</v>
+      </c>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3">
-        <v>5</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="C24" s="3">
+        <v>10</v>
+      </c>
+      <c r="D24" s="3">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3">
+        <v>6</v>
+      </c>
+      <c r="G24" s="3">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3">
-        <v>4</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2">
-        <v>4</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="C25" s="3">
+        <v>10</v>
+      </c>
+      <c r="D25" s="3">
+        <v>5</v>
+      </c>
       <c r="E25" s="3">
-        <v>2</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="F25" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="G25" s="3">
+        <f t="shared" si="0"/>
+        <v>24.5</v>
+      </c>
+      <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="2">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2">
+        <v>4</v>
+      </c>
+      <c r="G26" s="2">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="H26" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="2">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <v>2</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="H27" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2">
-        <v>3</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+      <c r="C28" s="3">
+        <v>10</v>
+      </c>
+      <c r="D28" s="3">
+        <v>5</v>
+      </c>
+      <c r="E28" s="3">
+        <v>5</v>
+      </c>
+      <c r="F28" s="3">
+        <v>7</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="3">
+        <v>10</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>4</v>
+      </c>
+      <c r="F29" s="3">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="3">
+        <v>10</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3">
+        <v>4</v>
+      </c>
+      <c r="F30" s="3">
+        <v>5</v>
+      </c>
+      <c r="G30" s="3">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>29</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="3">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3">
+        <v>5</v>
+      </c>
+      <c r="E31" s="3">
+        <v>4</v>
+      </c>
+      <c r="F31" s="3">
+        <v>10</v>
+      </c>
+      <c r="G31" s="3">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="3">
+        <v>10</v>
+      </c>
+      <c r="D32" s="3">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="F32" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="3">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
+        <v>6</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3">
-        <v>5</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2">
-        <v>4</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3">
-        <v>4</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3">
-        <v>4</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1" t="s">
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1">
-        <v>5</v>
-      </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2">
-        <v>2</v>
-      </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="C34" s="3">
+        <v>10</v>
+      </c>
+      <c r="D34" s="3">
+        <v>3</v>
+      </c>
+      <c r="E34" s="3">
+        <v>2</v>
+      </c>
+      <c r="F34" s="3">
+        <v>5</v>
+      </c>
+      <c r="G34" s="3">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
+      <c r="B35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="3">
+        <v>10</v>
+      </c>
+      <c r="D35" s="3">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3">
+        <v>6</v>
+      </c>
+      <c r="G35" s="3">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F36" t="s">
+        <v>78</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Notas - 1º etapa.xlsx
+++ b/Notas - 1º etapa.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polia\OneDrive\Desktop\Edgar da Mata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mobili\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E38DBC1-5D28-48E1-8A65-61AEB36EAE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B5023C-71FE-4D81-BE24-51E18018D2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FE5C7E3B-0CF7-4B17-BC8B-315FA1CE83BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FE5C7E3B-0CF7-4B17-BC8B-315FA1CE83BF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
-    <sheet name="Planilha3" sheetId="3" r:id="rId3"/>
+    <sheet name="Matematica_4A" sheetId="1" r:id="rId1"/>
+    <sheet name="Matemtica_4B" sheetId="2" r:id="rId2"/>
+    <sheet name="Ciências_4B" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -726,19 +726,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{265D5763-796C-4A95-880D-F96959D985BE}">
   <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" customWidth="1"/>
-    <col min="2" max="2" width="39.21875" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="11.77734375" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="5.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>81</v>
       </c>
@@ -751,7 +751,7 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>77</v>
       </c>
@@ -765,7 +765,7 @@
       <c r="I3" s="9"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>80</v>
       </c>
@@ -778,7 +778,7 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>0</v>
       </c>
@@ -809,7 +809,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -838,7 +838,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -869,7 +869,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -898,7 +898,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -929,7 +929,7 @@
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -960,7 +960,7 @@
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>6</v>
       </c>
@@ -989,7 +989,7 @@
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -1020,7 +1020,7 @@
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>8</v>
       </c>
@@ -1049,7 +1049,7 @@
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>9</v>
       </c>
@@ -1080,7 +1080,7 @@
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>10</v>
       </c>
@@ -1109,7 +1109,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>11</v>
       </c>
@@ -1140,7 +1140,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>12</v>
       </c>
@@ -1171,7 +1171,7 @@
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>13</v>
       </c>
@@ -1202,7 +1202,7 @@
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>14</v>
       </c>
@@ -1233,7 +1233,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>15</v>
       </c>
@@ -1264,7 +1264,7 @@
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>16</v>
       </c>
@@ -1295,7 +1295,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>17</v>
       </c>
@@ -1324,7 +1324,7 @@
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>18</v>
       </c>
@@ -1353,7 +1353,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>19</v>
       </c>
@@ -1384,7 +1384,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>20</v>
       </c>
@@ -1415,7 +1415,7 @@
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>21</v>
       </c>
@@ -1446,7 +1446,7 @@
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>22</v>
       </c>
@@ -1477,7 +1477,7 @@
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>23</v>
       </c>
@@ -1508,7 +1508,7 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24</v>
       </c>
@@ -1539,7 +1539,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>25</v>
       </c>
@@ -1570,7 +1570,7 @@
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>26</v>
       </c>
@@ -1599,7 +1599,7 @@
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>27</v>
       </c>
@@ -1628,7 +1628,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>28</v>
       </c>
@@ -1659,7 +1659,7 @@
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>29</v>
       </c>
@@ -1690,7 +1690,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>30</v>
       </c>
@@ -1721,7 +1721,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>31</v>
       </c>
@@ -1736,7 +1736,7 @@
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>32</v>
       </c>
@@ -1751,7 +1751,7 @@
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>33</v>
       </c>
@@ -1779,18 +1779,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22808D7A-FF36-43BE-917F-22779B1C1497}">
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="18.21875" customWidth="1"/>
-    <col min="8" max="8" width="14.21875" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
@@ -1803,7 +1803,7 @@
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
     </row>
-    <row r="2" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>76</v>
       </c>
@@ -1816,7 +1816,7 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
     </row>
-    <row r="3" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>82</v>
       </c>
@@ -1829,7 +1829,7 @@
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="I31" s="3"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -2719,17 +2719,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B05A61D-8986-40ED-93C5-768E17F97F81}">
   <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="39.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="39.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
@@ -2741,7 +2741,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>75</v>
       </c>
@@ -2753,7 +2753,7 @@
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
     </row>
-    <row r="3" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>83</v>
       </c>
@@ -2765,7 +2765,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F36" t="s">
         <v>78</v>
       </c>

--- a/Notas - 1º etapa.xlsx
+++ b/Notas - 1º etapa.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mobili\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polia\OneDrive\Desktop\Edgar da Mata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B5023C-71FE-4D81-BE24-51E18018D2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E38DBC1-5D28-48E1-8A65-61AEB36EAE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FE5C7E3B-0CF7-4B17-BC8B-315FA1CE83BF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FE5C7E3B-0CF7-4B17-BC8B-315FA1CE83BF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Matematica_4A" sheetId="1" r:id="rId1"/>
-    <sheet name="Matemtica_4B" sheetId="2" r:id="rId2"/>
-    <sheet name="Ciências_4B" sheetId="3" r:id="rId3"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
+    <sheet name="Planilha3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -726,19 +726,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{265D5763-796C-4A95-880D-F96959D985BE}">
   <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="39.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="39.21875" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="5.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>81</v>
       </c>
@@ -751,7 +751,7 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>77</v>
       </c>
@@ -765,7 +765,7 @@
       <c r="I3" s="9"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:11" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>80</v>
       </c>
@@ -778,7 +778,7 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>0</v>
       </c>
@@ -809,7 +809,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -838,7 +838,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -869,7 +869,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -898,7 +898,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -929,7 +929,7 @@
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -960,7 +960,7 @@
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>6</v>
       </c>
@@ -989,7 +989,7 @@
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -1020,7 +1020,7 @@
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>8</v>
       </c>
@@ -1049,7 +1049,7 @@
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>9</v>
       </c>
@@ -1080,7 +1080,7 @@
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>10</v>
       </c>
@@ -1109,7 +1109,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>11</v>
       </c>
@@ -1140,7 +1140,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>12</v>
       </c>
@@ -1171,7 +1171,7 @@
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>13</v>
       </c>
@@ -1202,7 +1202,7 @@
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>14</v>
       </c>
@@ -1233,7 +1233,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>15</v>
       </c>
@@ -1264,7 +1264,7 @@
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>16</v>
       </c>
@@ -1295,7 +1295,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>17</v>
       </c>
@@ -1324,7 +1324,7 @@
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>18</v>
       </c>
@@ -1353,7 +1353,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>19</v>
       </c>
@@ -1384,7 +1384,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>20</v>
       </c>
@@ -1415,7 +1415,7 @@
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>21</v>
       </c>
@@ -1446,7 +1446,7 @@
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>22</v>
       </c>
@@ -1477,7 +1477,7 @@
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>23</v>
       </c>
@@ -1508,7 +1508,7 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>24</v>
       </c>
@@ -1539,7 +1539,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>25</v>
       </c>
@@ -1570,7 +1570,7 @@
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>26</v>
       </c>
@@ -1599,7 +1599,7 @@
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>27</v>
       </c>
@@ -1628,7 +1628,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>28</v>
       </c>
@@ -1659,7 +1659,7 @@
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>29</v>
       </c>
@@ -1690,7 +1690,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>30</v>
       </c>
@@ -1721,7 +1721,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>31</v>
       </c>
@@ -1736,7 +1736,7 @@
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>32</v>
       </c>
@@ -1751,7 +1751,7 @@
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>33</v>
       </c>
@@ -1779,18 +1779,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22808D7A-FF36-43BE-917F-22779B1C1497}">
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
@@ -1803,7 +1803,7 @@
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
     </row>
-    <row r="2" spans="1:9" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>76</v>
       </c>
@@ -1816,7 +1816,7 @@
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
     </row>
-    <row r="3" spans="1:9" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>82</v>
       </c>
@@ -1829,7 +1829,7 @@
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="I31" s="3"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -2719,17 +2719,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B05A61D-8986-40ED-93C5-768E17F97F81}">
   <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="39.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.77734375" customWidth="1"/>
+    <col min="2" max="2" width="39.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
@@ -2741,7 +2741,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>75</v>
       </c>
@@ -2753,7 +2753,7 @@
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
     </row>
-    <row r="3" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>83</v>
       </c>
@@ -2765,7 +2765,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F36" t="s">
         <v>78</v>
       </c>
